--- a/journal_analyzer/brantree/task_list_brantree.xlsx
+++ b/journal_analyzer/brantree/task_list_brantree.xlsx
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>계정과목 / 금액열 / 최소금액 / 실행여부 / 비고</t>
+          <t>계정과목 / 금액열(차변·대변·both) / 최소금액 / 실행여부 / 비고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정과목 (선택: 개수 / 금액열 열 추가 가능)</t>
+          <t>계정과목 (선택: 개수 / 금액열(차변·대변·both) 열 추가 가능)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>작업명 / 계정과목 / 거래처명 / 금액열 / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
+          <t>작업명 / 계정과목 / 거래처명 / 금액열(차변·대변·both) / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>계정과목 / 금액유형(차변·대변·차변대변모두) / 실행여부</t>
+          <t>계정과목 / 금액유형(차변·대변·both) / 실행여부</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/brantree/task_list_brantree.xlsx
+++ b/journal_analyzer/brantree/task_list_brantree.xlsx
@@ -93,7 +93,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -103,6 +103,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -696,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -723,8 +724,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -801,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="19.08203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -819,7 +818,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -831,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
@@ -846,8 +844,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4" ht="18.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -860,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -873,24 +869,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -902,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16.25" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -925,10 +903,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -966,7 +940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1005,12 +979,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="G8" s="3" t="n"/>
     </row>
@@ -1302,9 +1270,6 @@
     <row r="104">
       <c r="G104" s="3" t="n"/>
     </row>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="손익구분 오류" error="목록에 없는 값입니다. 매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택하세요." promptTitle="손익구분 선택" prompt="매출/매출원가/판관비/제조원가/영업외수익/영업외비용 중 선택" type="list">
@@ -1323,28 +1288,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="13.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>샘플링비율</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>최소건수</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>최대건수</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>금액상위</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>최신</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>이상치</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>월별</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>랜덤</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>중점검토사항</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1356,7 +1372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1389,14 +1405,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1996,12 +2004,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>계정과목 / 실행여부</t>
+          <t>계정과목 / 실행여부 / 샘플링비율 / 최소건수 / 최대건수 / 금액상위 / 최신 / 이상치 / 월별 / 랜덤 / 중점검토사항(선택)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>.env에 GEMINI_API_KEY 필요 (Gemini 실제 호출, 비용 발생)</t>
+          <t>.env에 GEMINI_API_KEY 필요 (Gemini 실제 호출, 계정 1행당 1회 호출·비용 발생). 샘플크기 = 당기 거래건수 × 샘플링비율(최소~최대건수로 제한). 구성비(금액상위/최신/이상치/월별/랜덤)는 합계 100% 기준이며 합이 달라도 비율대로 자동 환산. 이상치 = 주말전기·금액이상치(IQR)·라운드금액(100만원 단위)·1회성거래처·적요미기재. 빈 칸은 기본값(5%, 30~150건, 30/20/10/30/10%). 중점검토사항에 적은 내용은 AI 분석 지시에 추가됨. 분석목록 26번 분석대상을 "전체"로 두면 전기 동기간 비교가 들어감(샘플은 당기에서만 추출)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>결과 시트 하나로 출력: 샘플링 / 계정요약 / 거래특징 / 경영자주장별 위험요소 / 감사인 제언 / 종합결론 / 확인필요전표 / 샘플내역 / 가명대조. AI에는 거래처·적요 속 실명은 가명, 직함 앞 사람이름·계좌번호는 마스킹해서 전송</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2171,15 +2184,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2191,7 +2195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.33203125" bestFit="1" customWidth="1" min="1" max="2"/>
@@ -2221,7 +2225,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2884,7 +2887,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립 실행)</t>
+          <t>계정별 스마트샘플(비율·구성 지정) + 통계를 Gemini로 분석 — 계정요약/거래특징/경영자주장별 위험/감사인 제언</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2894,7 +2897,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전체</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2974,22 +2977,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -3084,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="15.08203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3140,10 +3127,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3215,7 +3198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3233,9 +3216,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3247,7 +3227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -3271,65 +3251,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/journal_analyzer/brantree/task_list_brantree.xlsx
+++ b/journal_analyzer/brantree/task_list_brantree.xlsx
@@ -17,17 +17,18 @@
     <sheet name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="17_거래처분석" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="21_총계정원장" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="22_은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="23_계정별 상세거래내역" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="24_리스완전성" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="25_손익월별분석" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="26_AI계정별분석_실행" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="27_감가상각_평가손익분석" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="유형자산_처분손익" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="15_감사샘플링" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="17_거래처분석" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="23_계정별 상세거래내역" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="24_리스완전성" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="25_손익월별분석" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="26_AI계정별분석_실행" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="27_감가상각_평가손익분석" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -36,9 +37,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -93,7 +95,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +106,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -735,6 +740,490 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>종료일</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>샘플링방법</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>금액타입</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>샘플크기</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>통계표사용</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>신뢰수준</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>허용왜곡표시</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>예상왜곡표시</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>이상거래포함</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>개별유의금액</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>예시) 매출 실재성 — 차변 MUS 30건</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>체계적</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>예시) 출금 증빙 — 대변 체계적 40건</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>예시) 통계표로 크기 계산 + 1천만원 이상 전수</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"MUS,체계적,무작위,금액상위"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"차변,대변,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B200 H2:H200 L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
@@ -794,7 +1283,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -823,7 +1312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -850,7 +1339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -874,7 +1363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -908,7 +1397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -934,7 +1423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1282,7 +1771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1366,50 +1855,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>그룹기준열</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1774,17 +2219,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI계정별분석 (시트 미생성)</t>
+          <t>감사샘플링</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>계정과목 / 실행여부</t>
+          <t>계정과목 / 실행여부 / 시작일·종료일(선택) / 샘플링방법(MUS·체계적·무작위·금액상위) / 금액타입(차변·대변·both) / 샘플크기 / 통계표사용(Y/N) / 신뢰수준 / 허용왜곡표시 / 예상왜곡표시 / 이상거래포함(Y/N) / 개별유의금액(선택)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>쓰려면 시트명을 정확히 'AI계정별분석'으로 새로 만들고 계정과목 입력. Gemini 호출 없이 월별추이·샘플만 추출(26번과 형식은 같으나 AI 분석은 안 함)</t>
+          <t>계정 1줄 = 샘플링 1건, 샘플은 해당 계정의 전표 줄 단위(같은 전표의 상대계정 줄은 뽑지 않고 상대계정 열에 참고 표시). MUS=금액 누적 기준 구간마다 1건(구간보다 큰 줄은 반드시 선택) / 체계적=건수 기준 일정 간격 / 무작위 / 금액상위. 통계표사용=Y면 샘플크기 = 모집단금액×신뢰계수÷(허용왜곡표시−예상왜곡표시×확장계수) (95%: 3.0·1.6, 90%: 2.31·1.5). 이상거래포함=Y면 Z-score 3 이상·최대값을 샘플크기 안에서 우선 포함. 개별유의금액 이상은 샘플크기와 별도로 전수 포함. 시드 고정(42)이라 다시 돌려도 같은 샘플</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>결과: 샘플링조건(모집단·원장대사·크기근거·커버리지) + 계정별 샘플 시트(증빙종류·증빙확인·승인확인·예외사항·확인자 빈칸). AI로 보내지 않으므로 거래처·적요 실명 출력</t>
         </is>
       </c>
     </row>
@@ -2130,6 +2580,50 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="21" bestFit="1" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>그룹기준열</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2189,7 +2683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2607,12 +3101,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI 계정별 분석</t>
+          <t>감사샘플링</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
+          <t>계정별 감사증빙 샘플 추출 (MUS/체계적/무작위/금액상위, 전표 줄 단위) → 15_감사샘플링 시트 참조</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">

--- a/journal_analyzer/brantree/task_list_brantree.xlsx
+++ b/journal_analyzer/brantree/task_list_brantree.xlsx
@@ -42,7 +42,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -71,13 +71,30 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00305496"/>
+    </font>
+    <font>
+      <color rgb="00404040"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -95,7 +112,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -109,6 +126,9 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1087,94 +1107,209 @@
       <c r="D30" s="8" t="n"/>
     </row>
     <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>■ 15번 감사샘플링 작성 안내 (이 안내 행들은 실행여부가 비어 있어 분석에 읽히지 않음 — 지우지 말고 위쪽 행에 계정 입력)</t>
+        </is>
+      </c>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="n"/>
     </row>
     <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>[기본 항목]</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="n"/>
     </row>
     <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>· 실행여부: Y(또는 O)인 행만 실행.  · 시작일/종료일: 비우면 분개장 전체 기간.</t>
+        </is>
+      </c>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="n"/>
     </row>
     <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>· 샘플링방법: MUS / 체계적 / 무작위 / 금액상위 (빈칸 = MUS).</t>
+        </is>
+      </c>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="n"/>
     </row>
     <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>· 금액타입: 차변 / 대변 / both (빈칸·그 외 값 = both). 결과시트명은 계정명_차 / _대 / _양.</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
     </row>
     <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>[샘플크기 — 통계표사용에 따라 결정]</t>
+        </is>
+      </c>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="n"/>
     </row>
     <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>· 통계표사용 = N(또는 빈칸): 샘플크기 칸의 입력값대로 추출 (빈칸 = 30건). 신뢰수준·허용/예상왜곡표시는 무시됨.</t>
+        </is>
+      </c>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
     </row>
     <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>· 통계표사용 = Y: 샘플크기 = 모집단금액 × 신뢰계수 ÷ (허용왜곡표시 − 예상왜곡표시 × 확장계수) 로 자동 계산, 샘플크기 칸 입력값은 무시됨.</t>
+        </is>
+      </c>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
     </row>
     <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 신뢰계수/확장계수: 90% = 2.31/1.5, 95% = 3.00/1.6, 99% = 4.61/1.9 (모집단금액은 개별유의금액 전수분을 뺀 금액).</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
     </row>
     <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>· 신뢰수준: 0.95 또는 95 둘 다 가능 (빈칸 = 0.95). 90/95/99% 중 가까운 값 적용.</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
     </row>
     <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>· 허용왜곡표시: 통계표사용 = Y이면 필수(예: 수행중요성). 비우면 해당 계정은 샘플 미추출 → 샘플링조건 시트 결과시트 "미추출" + 비고에 사유 표시.</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="n"/>
     </row>
     <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>· 예상왜곡표시: 비워도 됨(빈칸 = 0). 0이면 샘플크기가 가장 작게 나오고, 전기 왜곡표시 등 오류 위험이 있으면 금액을 넣어 보수적으로(샘플 증가).</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
     </row>
     <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 예상왜곡표시 × 확장계수 ≥ 허용왜곡표시 이면 계산 불가 → 해당 계정 건너뛰고 비고에 사유 표시.</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="n"/>
     </row>
     <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>[금액 입력 형식 — 허용왜곡표시·예상왜곡표시·개별유의금액]</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>· 원 단위 숫자로 입력: 500000000 또는 500,000,000 (엑셀 숫자 셀 OK).</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="n"/>
     </row>
     <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>· "5억", "500,000,000원"처럼 글자가 섞이면 빈칸으로 처리됨. "5%", 0.05 같은 비율 입력 금지(5원·0.05원으로 읽힘).</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="n"/>
     </row>
     <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>[추가 옵션]</t>
+        </is>
+      </c>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="n"/>
     </row>
     <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>· 개별유의금액: 이 금액 이상인 줄은 전수 추출(샘플크기와 별도로 추가). 빈칸 = 전수 없음.</t>
+        </is>
+      </c>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
     </row>
     <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>· 이상거래포함 = Y: 최대값 + Z-score 3 이상 거래를 샘플크기의 20%까지 먼저 포함(샘플크기 안에 포함됨).</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
     </row>
     <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>[결과 확인]</t>
+        </is>
+      </c>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
     </row>
     <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>· 샘플링조건 시트: 계정별 모집단·원장 대사·샘플크기 근거·추출조건 요약. 샘플 시트가 안 나오면 이 시트의 결과시트·비고 열부터 확인.</t>
+        </is>
+      </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
     </row>
     <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>· 샘플 단위는 해당 계정의 전표 "줄". 같은 전표의 상대계정 줄은 뽑지 않고 상대계정 열에 참고로만 표시.</t>
+        </is>
+      </c>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
     </row>
     <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>· 시드 42 고정 → 같은 조건으로 재실행하면 같은 샘플(조서 재현성). 증빙종류~확인자 열은 감사인이 직접 기재.</t>
+        </is>
+      </c>
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="n"/>
     </row>

--- a/journal_analyzer/brantree/task_list_brantree.xlsx
+++ b/journal_analyzer/brantree/task_list_brantree.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="12" activeTab="15" autoFilterDateGrouping="1"/>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="분석목록" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="02_거래처 전기_당기 비교" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="03_벤포드 분석" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="08_상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="10_라운드넘버 분석" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="15_감사샘플링" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="17_거래처분석" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="23_계정별 상세거래내역" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="24_리스완전성" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="25_손익월별분석" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="26_AI계정별분석_실행" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="27_감가상각_평가손익분석" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석목록" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_거래처 전기_당기 비교" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_벤포드 분석" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_라운드넘버 분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_감사샘플링" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_거래처분석" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_계정별 상세거래내역" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_리스완전성" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_손익월별분석" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_AI계정별분석_실행" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_감가상각_평가손익분석" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -284,20 +284,25 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>차변/대변/both 중 하나 — 상세내역·월별합산에 포함할 금액 방향. 공란이면 자동으로 both(차변+대변 모두) 처리됨</t>
+        <t>원장 적요에 포함된 문구(부분일치), 콤마(,)로 여러 개 지정 가능(OR). 기재하면 계정과목·거래처명·금액열 조건에 더해 적요 조건까지 만족하는 거래만 추출. 공란이면 적요 조건 없이 기존처럼 추출. 거래처명을 비우고 적요만 적으면 적요 기준으로 추출(거래처별 시트는 적요 문구별로 생성)</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Y(또는 O)로 표시한 행만 분석에 포함됨</t>
+        <t>차변/대변/both 중 하나 — 상세내역·월별합산에 포함할 금액 방향. 공란이면 자동으로 both(차변+대변 모두) 처리됨</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
+        <t>Y(또는 O)로 표시한 행만 분석에 포함됨</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
         <t>Y로 지정하면 이 작업의 월별합산 결과를 전표관리단위(본사/2공장 등)별로도 나눠서 함께 추출 (공란=기존처럼 단위 구분 없이 합산)</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>Y로 지정하면 이 작업의 월별합산 결과를 비용구분(판관/제조 등)별로도 나눠서 함께 추출 (공란=기존처럼 구분 없이 합산)</t>
       </text>
@@ -1359,13 +1364,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="27.75" customWidth="1" min="1" max="1"/>
-    <col width="26.9140625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="35.25" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="5" max="7"/>
+    <col width="26.9140625" customWidth="1" min="2" max="2"/>
+    <col width="35.25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1386,20 +1392,25 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>적요</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>금액열</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>관리단위</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>비용구분</t>
         </is>
@@ -1408,7 +1419,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
+          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명·적요는 콤마로 여러 개 가능 / 적요 기재 시 적요 조건도 추가(공란=조건 없음) / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
